--- a/src/main/resources/Program_Field_Values_Test8.xlsx
+++ b/src/main/resources/Program_Field_Values_Test8.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89FB0CF-D987-4D4E-BA3B-F4BB8F1199DB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4443482F-46CE-4138-ACAA-9578D349A6D1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,7 +12,7 @@
     <sheet name="Creation1" sheetId="6" r:id="rId2"/>
     <sheet name="Edition1" sheetId="7" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
-    <sheet name="Edition" sheetId="4" r:id="rId5"/>
+    <sheet name="EditionProgram" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="30">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -62,15 +62,6 @@
     <t>Overview</t>
   </si>
   <si>
-    <t>Abbreviation__c</t>
-  </si>
-  <si>
-    <t>WebsiteAddress__c</t>
-  </si>
-  <si>
-    <t>http://automate.com</t>
-  </si>
-  <si>
     <t>Objectives__c</t>
   </si>
   <si>
@@ -96,9 +87,6 @@
   </si>
   <si>
     <t>ProgramName__c</t>
-  </si>
-  <si>
-    <t>PREG</t>
   </si>
   <si>
     <t>Community Health &amp; Equity</t>
@@ -484,10 +472,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -509,7 +497,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -517,10 +505,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -528,10 +516,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -539,10 +527,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -550,7 +538,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -561,7 +549,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>365</v>
@@ -601,10 +589,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -626,7 +614,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -634,10 +622,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -645,10 +633,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -656,10 +644,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -667,7 +655,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -675,7 +663,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>123</v>
@@ -686,7 +674,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -697,7 +685,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C11">
         <v>365</v>
@@ -735,10 +723,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -746,10 +734,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -757,10 +745,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -806,7 +794,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -831,7 +819,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
@@ -857,36 +845,11 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{2964AC08-382B-4FAE-8F45-970C952B4A4E}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values_Test8.xlsx
+++ b/src/main/resources/Program_Field_Values_Test8.xlsx
@@ -3,16 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4443482F-46CE-4138-ACAA-9578D349A6D1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E076ACEC-F372-4346-9D8E-041EC5CB01BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
-    <sheet name="Creation1" sheetId="6" r:id="rId2"/>
-    <sheet name="Edition1" sheetId="7" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
-    <sheet name="EditionProgram" sheetId="4" r:id="rId5"/>
+    <sheet name="EditionProgram" sheetId="4" r:id="rId2"/>
+    <sheet name="CompetitiveAnnouncement" sheetId="5" r:id="rId3"/>
+    <sheet name="Creation Second Modal" sheetId="8" r:id="rId4"/>
+    <sheet name="EditionAnn" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -24,38 +24,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
   <si>
     <t>Sub Tab</t>
   </si>
   <si>
-    <t>Field Type</t>
-  </si>
-  <si>
     <t>Field Value</t>
   </si>
   <si>
     <t>Field API Name</t>
   </si>
   <si>
-    <t>Text</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
-    <t>Dropdown</t>
-  </si>
-  <si>
     <t>Type__c</t>
   </si>
   <si>
     <t>Project Grants</t>
   </si>
   <si>
-    <t>Lookup</t>
-  </si>
-  <si>
     <t>PrimaryFundingOrganization__c</t>
   </si>
   <si>
@@ -65,18 +53,12 @@
     <t>Objectives__c</t>
   </si>
   <si>
-    <t>RichText</t>
-  </si>
-  <si>
     <t>Automation test description</t>
   </si>
   <si>
     <t>FocusAreaRequired__c</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>KPIsRequired__c</t>
   </si>
   <si>
@@ -89,24 +71,9 @@
     <t>ProgramName__c</t>
   </si>
   <si>
-    <t>Community Health &amp; Equity</t>
-  </si>
-  <si>
-    <t>fieldAccount__c</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Automation Runtime Execution Internal Program in another ORG</t>
-  </si>
-  <si>
-    <t>FederalProgramCFDA__c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StartDate__c	</t>
-  </si>
-  <si>
     <t>EndDate__c</t>
   </si>
   <si>
@@ -114,6 +81,75 @@
   </si>
   <si>
     <t>Automation Internal Program for flow</t>
+  </si>
+  <si>
+    <t>AnnouncementName__c</t>
+  </si>
+  <si>
+    <t>Program__c</t>
+  </si>
+  <si>
+    <t>Budget_Category_Package__c</t>
+  </si>
+  <si>
+    <t>Non-Construction</t>
+  </si>
+  <si>
+    <t>IsMatchRequired__c</t>
+  </si>
+  <si>
+    <t>LaverageAllowed__c</t>
+  </si>
+  <si>
+    <t>IsProgramIncomeAnticipated__c</t>
+  </si>
+  <si>
+    <t>PreApplicationNeeded__c</t>
+  </si>
+  <si>
+    <t>WBSRequired__c</t>
+  </si>
+  <si>
+    <t>RiskAssessment_Required__c</t>
+  </si>
+  <si>
+    <t>AreExpensesBuildIUpLevel__c</t>
+  </si>
+  <si>
+    <t>IsAdvancePermitted__c</t>
+  </si>
+  <si>
+    <t>IsNegotiationsAllowed__c</t>
+  </si>
+  <si>
+    <t>AnnouncementDescription__c</t>
+  </si>
+  <si>
+    <t>EligibleApplicantTypes__c</t>
+  </si>
+  <si>
+    <t>State governments;Independent school districts</t>
+  </si>
+  <si>
+    <t>ApplicationDueDate__c</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>AwardFloor__c</t>
+  </si>
+  <si>
+    <t>AwardCeiling__c</t>
+  </si>
+  <si>
+    <t>EstimatedNumberOfAwards__c</t>
+  </si>
+  <si>
+    <t>TotalCommittedAmount__c</t>
+  </si>
+  <si>
+    <t>Automation Internal Announcement for flow</t>
   </si>
 </sst>
 </file>
@@ -461,84 +497,84 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -546,10 +582,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>365</v>
@@ -565,259 +601,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11">
-        <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -831,25 +614,346 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="33.85546875" customWidth="1"/>
+    <col min="3" max="3" width="56.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB7E775-FC9D-4F7A-8132-7FE7649A7A48}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C20002D2-73D8-4767-9B06-FA8D83AF8B94}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" customWidth="1"/>
+    <col min="3" max="3" width="46.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8">
+        <v>10000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values_Test8.xlsx
+++ b/src/main/resources/Program_Field_Values_Test8.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E076ACEC-F372-4346-9D8E-041EC5CB01BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C034F4F-C5A1-4BA6-AE28-6C8207B99283}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -606,7 +606,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/Program_Field_Values_Test8.xlsx
+++ b/src/main/resources/Program_Field_Values_Test8.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C034F4F-C5A1-4BA6-AE28-6C8207B99283}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC43D8C7-BD6A-4B7D-BCD1-6F1865F5ED36}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -13,6 +13,9 @@
     <sheet name="CompetitiveAnnouncement" sheetId="5" r:id="rId3"/>
     <sheet name="Creation Second Modal" sheetId="8" r:id="rId4"/>
     <sheet name="EditionAnn" sheetId="9" r:id="rId5"/>
+    <sheet name="AppEdition" sheetId="10" r:id="rId6"/>
+    <sheet name="Form Fields 1" sheetId="11" r:id="rId7"/>
+    <sheet name="Form Fields 2" sheetId="12" r:id="rId8"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -24,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="71">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -150,6 +153,93 @@
   </si>
   <si>
     <t>Automation Internal Announcement for flow</t>
+  </si>
+  <si>
+    <t>fieldProjectAbstract__c</t>
+  </si>
+  <si>
+    <t>Automation application Project abstract</t>
+  </si>
+  <si>
+    <t>fieldAcknowledgment4__c</t>
+  </si>
+  <si>
+    <t>Checked</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>fieldJustification__c</t>
+  </si>
+  <si>
+    <t>Justified</t>
+  </si>
+  <si>
+    <t>Proposal</t>
+  </si>
+  <si>
+    <t>fieldApproachMethodology__c</t>
+  </si>
+  <si>
+    <t>Automation Test Description</t>
+  </si>
+  <si>
+    <t>fieldCapacity__c</t>
+  </si>
+  <si>
+    <t>fieldQualifications__c</t>
+  </si>
+  <si>
+    <t>SubmittedOnForm__c</t>
+  </si>
+  <si>
+    <t>AppplicationSubmitted__c</t>
+  </si>
+  <si>
+    <t>Automation SPI</t>
+  </si>
+  <si>
+    <t>Question1__c</t>
+  </si>
+  <si>
+    <t>Describe the activities and/or services to be provided</t>
+  </si>
+  <si>
+    <t>Question2__c</t>
+  </si>
+  <si>
+    <t>Describe the methodologies that will be used to complete activities/provide services</t>
+  </si>
+  <si>
+    <t>Question3__c</t>
+  </si>
+  <si>
+    <t>Describe how the project will be completed within the required 24-month timeline.</t>
+  </si>
+  <si>
+    <t>Question4__c</t>
+  </si>
+  <si>
+    <t>Question5__c</t>
+  </si>
+  <si>
+    <t>Question6__c</t>
+  </si>
+  <si>
+    <t>Question7__c</t>
+  </si>
+  <si>
+    <t>Question8__c</t>
+  </si>
+  <si>
+    <t>Question9__c</t>
+  </si>
+  <si>
+    <t>Question10__c</t>
+  </si>
+  <si>
+    <t>Question11__c</t>
   </si>
 </sst>
 </file>
@@ -956,4 +1046,289 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE65A359-5AAB-4789-BD03-7AE892333B23}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B07CBE-222D-4AEE-8FCA-38CFE50B7B5A}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DC0711-B086-4AFD-A039-B2CBB4A4E899}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values_Test8.xlsx
+++ b/src/main/resources/Program_Field_Values_Test8.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC43D8C7-BD6A-4B7D-BCD1-6F1865F5ED36}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF84ADA-221A-4D61-B7A9-818014083707}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -16,6 +16,15 @@
     <sheet name="AppEdition" sheetId="10" r:id="rId6"/>
     <sheet name="Form Fields 1" sheetId="11" r:id="rId7"/>
     <sheet name="Form Fields 2" sheetId="12" r:id="rId8"/>
+    <sheet name="Payment Request Schedule" sheetId="18" r:id="rId9"/>
+    <sheet name="Payment Request Schedule_FDM" sheetId="13" r:id="rId10"/>
+    <sheet name="Progress Report Schedule_FDM" sheetId="14" r:id="rId11"/>
+    <sheet name="Grant_Creation" sheetId="15" r:id="rId12"/>
+    <sheet name="Grant_Edition" sheetId="16" r:id="rId13"/>
+    <sheet name="Edition_StandAlone" sheetId="17" r:id="rId14"/>
+    <sheet name="Site Visit" sheetId="19" r:id="rId15"/>
+    <sheet name="Edition_Site_Visit" sheetId="20" r:id="rId16"/>
+    <sheet name="Form Fields" sheetId="21" r:id="rId17"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -27,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="132">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -240,13 +249,196 @@
   </si>
   <si>
     <t>Question11__c</t>
+  </si>
+  <si>
+    <t>SubmissionTitle__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Runtime Payment Request </t>
+  </si>
+  <si>
+    <t>ScheduleBase__c</t>
+  </si>
+  <si>
+    <t>Reporting Period</t>
+  </si>
+  <si>
+    <t>Frequency__c</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Runtime Progress Report </t>
+  </si>
+  <si>
+    <t>fieldProjectTitle__c</t>
+  </si>
+  <si>
+    <t>GrantAbbreviation__c</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>ProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>BudgetCategoryPackage__c</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>fieldInternalOrganization__c</t>
+  </si>
+  <si>
+    <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
+  </si>
+  <si>
+    <t>Automation Permanent Internal Program</t>
+  </si>
+  <si>
+    <t>ExternalOrganization__c</t>
+  </si>
+  <si>
+    <t>IsBuildUpFunctionality__c</t>
+  </si>
+  <si>
+    <t>RiskAssessmentRequired__c</t>
+  </si>
+  <si>
+    <t>GrantAwardDescription__c</t>
+  </si>
+  <si>
+    <t>BudgetPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>11/29/2020 06:36 PM</t>
+  </si>
+  <si>
+    <t>Automation Runtime Payment Request</t>
+  </si>
+  <si>
+    <t>CalReportingStartDate__c</t>
+  </si>
+  <si>
+    <t>CalReportingEndDate__c</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
+  </si>
+  <si>
+    <t>Automation Direct Grant</t>
+  </si>
+  <si>
+    <t>Title__c</t>
+  </si>
+  <si>
+    <t>Automation Runtime Site Visit</t>
+  </si>
+  <si>
+    <t>GranteePOCContact__c</t>
+  </si>
+  <si>
+    <t>MonitoringType__c</t>
+  </si>
+  <si>
+    <t>Program &amp; Fiscal</t>
+  </si>
+  <si>
+    <t>VisitDateandTime__c</t>
+  </si>
+  <si>
+    <t>VisitEndDateTime__c</t>
+  </si>
+  <si>
+    <t>fieldDescription__c</t>
+  </si>
+  <si>
+    <t>Automation Test description</t>
+  </si>
+  <si>
+    <t>fieldPointsdiscussedwithofficials__c</t>
+  </si>
+  <si>
+    <t>fieldSiteVisitPurpose__c</t>
+  </si>
+  <si>
+    <t>Routine based on monitoring responsibilities</t>
+  </si>
+  <si>
+    <t>fieldSourceSiteVisit__c</t>
+  </si>
+  <si>
+    <t>To fulfill pass-through monitoring responsibilities</t>
+  </si>
+  <si>
+    <t>fieldSupportingCommentsQuestion1__c</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ1__c</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ2__c</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ3__c</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ4__c</t>
+  </si>
+  <si>
+    <t>1. Does the organization have current written program policies and procedures?</t>
+  </si>
+  <si>
+    <t>2. Does the applicant have a current organization chart?</t>
+  </si>
+  <si>
+    <t>3. Does the organization have adequate accounting and financial systems in place for grant management? </t>
+  </si>
+  <si>
+    <t>4. If the organization will have shared costs, has a cost allocation plan been provided?</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ5__c</t>
+  </si>
+  <si>
+    <t>5. If the organization has indirect costs, was an indirect cost agreement submitted, or are they using the 10% de minimis rate?</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ6__c</t>
+  </si>
+  <si>
+    <t>1. Are facilities adequate for the grant program activities?  If not, provide an explanation.</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ7__c</t>
+  </si>
+  <si>
+    <t>2. Are all equipment items adequate for the planned grant program activities? If not, provide an explanation.</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ8__c</t>
+  </si>
+  <si>
+    <t>1. Has the organization provided position descriptions for all grant-funded personnel?</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ9__c</t>
+  </si>
+  <si>
+    <t>2. If hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,6 +453,23 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -284,7 +493,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -293,6 +502,14 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -690,6 +907,716 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8AC423-05DF-4280-95EB-279829201824}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72FC2E7-798D-4A0D-9033-321F9F52B381}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4FD98F4-5D65-489F-B6B9-0B173C389D1A}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE56BC4D-8AEC-4E4E-85C8-89449AEEC07A}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CAF4D77-609A-474F-A16C-8985A05DDF89}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA29119-FFAC-4260-A292-75CB58842AAB}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD981C06-1D14-46F5-A3A9-915937C2A139}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DEDBD1-53EB-4D57-9108-0852043B1383}">
+  <dimension ref="A2:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C2"/>
@@ -1178,8 +2105,8 @@
       <c r="B3" t="s">
         <v>54</v>
       </c>
-      <c r="C3">
-        <v>0</v>
+      <c r="C3" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1331,4 +2258,84 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2D24CD-6391-4318-8144-E561BCF57A37}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values_Test8.xlsx
+++ b/src/main/resources/Program_Field_Values_Test8.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF84ADA-221A-4D61-B7A9-818014083707}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6D182B-6396-4FF3-9401-00562CA77ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="135">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -50,15 +50,9 @@
     <t>None</t>
   </si>
   <si>
-    <t>Type__c</t>
-  </si>
-  <si>
     <t>Project Grants</t>
   </si>
   <si>
-    <t>PrimaryFundingOrganization__c</t>
-  </si>
-  <si>
     <t>Overview</t>
   </si>
   <si>
@@ -80,18 +74,9 @@
     <t>Test Automation Organization</t>
   </si>
   <si>
-    <t>ProgramName__c</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
-    <t>EndDate__c</t>
-  </si>
-  <si>
-    <t>StartDate__c</t>
-  </si>
-  <si>
     <t>Automation Internal Program for flow</t>
   </si>
   <si>
@@ -432,6 +417,30 @@
   </si>
   <si>
     <t>2. If hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures?</t>
+  </si>
+  <si>
+    <t>fieldType__c</t>
+  </si>
+  <si>
+    <t>fieldEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldPrimaryFundingOrganization__c</t>
+  </si>
+  <si>
+    <t>fieldFocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>fieldProgramName__c</t>
+  </si>
+  <si>
+    <t>fieldIsGoalsRequired__c</t>
+  </si>
+  <si>
+    <t>fieldKPIsRequired__c</t>
   </si>
 </sst>
 </file>
@@ -795,7 +804,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" customWidth="1"/>
     <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -815,10 +824,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -826,10 +835,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -837,10 +846,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -848,10 +857,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -859,10 +868,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -870,10 +879,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -881,7 +890,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -892,7 +901,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C9">
         <v>365</v>
@@ -932,10 +941,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -943,10 +952,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -954,10 +963,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -994,10 +1003,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1005,10 +1014,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1016,10 +1025,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1052,10 +1061,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1063,10 +1072,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1074,7 +1083,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1085,7 +1094,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1096,10 +1105,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1107,10 +1116,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1118,10 +1127,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1129,10 +1138,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1166,10 +1175,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1177,10 +1186,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1188,10 +1197,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1199,10 +1208,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1210,10 +1219,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1221,10 +1230,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1232,10 +1241,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1243,10 +1252,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1254,10 +1263,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1265,10 +1274,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1276,10 +1285,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1311,21 +1320,21 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C3">
         <v>3650</v>
@@ -1361,10 +1370,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1372,10 +1381,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1383,10 +1392,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1417,10 +1426,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1428,10 +1437,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1439,57 +1448,57 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1518,10 +1527,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1529,10 +1538,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1540,10 +1549,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1551,10 +1560,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1562,10 +1571,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1573,10 +1582,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1584,10 +1593,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1595,10 +1604,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1606,10 +1615,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1639,13 +1648,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1680,10 +1689,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1691,10 +1700,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1702,10 +1711,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1739,10 +1748,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1750,10 +1759,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1761,10 +1770,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1772,10 +1781,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1783,10 +1792,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1794,10 +1803,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1805,10 +1814,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1816,10 +1825,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1827,10 +1836,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1838,10 +1847,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1849,10 +1858,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1860,10 +1869,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1894,32 +1903,32 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -1927,10 +1936,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>1000</v>
@@ -1938,10 +1947,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -1949,10 +1958,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -1960,10 +1969,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>10000</v>
@@ -1998,68 +2007,68 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2092,10 +2101,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2103,10 +2112,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2139,10 +2148,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2150,10 +2159,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2161,10 +2170,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2172,10 +2181,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2183,10 +2192,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2194,10 +2203,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2205,10 +2214,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2216,10 +2225,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2227,10 +2236,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2238,10 +2247,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2249,10 +2258,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2285,10 +2294,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2296,10 +2305,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2307,7 +2316,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2318,7 +2327,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2329,10 +2338,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values_Test8.xlsx
+++ b/src/main/resources/Program_Field_Values_Test8.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6D182B-6396-4FF3-9401-00562CA77ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219C241E-24AA-4D38-806E-DBFE50C5E726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="136">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -128,9 +128,6 @@
     <t>State governments;Independent school districts</t>
   </si>
   <si>
-    <t>ApplicationDueDate__c</t>
-  </si>
-  <si>
     <t>Financials</t>
   </si>
   <si>
@@ -441,6 +438,12 @@
   </si>
   <si>
     <t>fieldKPIsRequired__c</t>
+  </si>
+  <si>
+    <t>fieldApplicationDueDate__c</t>
+  </si>
+  <si>
+    <t>fieldProgram__c</t>
   </si>
 </sst>
 </file>
@@ -824,7 +827,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -835,7 +838,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -846,7 +849,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
@@ -857,7 +860,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -868,7 +871,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -879,7 +882,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -890,7 +893,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -901,7 +904,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C9">
         <v>365</v>
@@ -941,10 +944,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
         <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -952,10 +955,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
         <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -963,10 +966,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
         <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1003,10 +1006,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1014,10 +1017,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
         <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1025,10 +1028,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
         <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1061,10 +1064,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1075,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
         <v>74</v>
-      </c>
-      <c r="C3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,7 +1086,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1094,7 +1097,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1105,10 +1108,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" t="s">
         <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1116,10 +1119,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
         <v>80</v>
-      </c>
-      <c r="C7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1127,10 +1130,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1138,10 +1141,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1219,7 +1222,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1263,7 +1266,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -1285,7 +1288,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -1323,18 +1326,18 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3">
         <v>3650</v>
@@ -1370,10 +1373,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s">
         <v>94</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1381,10 +1384,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1392,10 +1395,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" t="s">
         <v>97</v>
-      </c>
-      <c r="C4" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1429,7 +1432,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1440,7 +1443,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1451,10 +1454,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
         <v>101</v>
-      </c>
-      <c r="C4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1462,10 +1465,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1473,10 +1476,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
         <v>104</v>
-      </c>
-      <c r="C6" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1484,10 +1487,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
         <v>106</v>
-      </c>
-      <c r="C7" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1495,10 +1498,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1527,10 +1530,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1538,10 +1541,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1549,10 +1552,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1560,10 +1563,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1571,10 +1574,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1582,10 +1585,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1593,10 +1596,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1604,10 +1607,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1615,10 +1618,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1692,7 +1695,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1928,7 +1931,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -1936,10 +1939,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
         <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
       </c>
       <c r="C5">
         <v>1000</v>
@@ -1947,10 +1950,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -1958,10 +1961,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -1969,10 +1972,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>10000</v>
@@ -2010,10 +2013,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
         <v>37</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2021,54 +2024,54 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
         <v>39</v>
-      </c>
-      <c r="C3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
         <v>41</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>45</v>
-      </c>
-      <c r="C5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2101,10 +2104,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2112,10 +2115,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2148,10 +2151,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2159,10 +2162,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
         <v>54</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2170,10 +2173,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
         <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2181,10 +2184,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2192,10 +2195,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2203,10 +2206,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2214,10 +2217,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2225,10 +2228,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2236,10 +2239,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2247,10 +2250,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2258,10 +2261,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2294,10 +2297,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2305,10 +2308,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
         <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2316,7 +2319,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2327,7 +2330,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2338,10 +2341,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
         <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values_Test8.xlsx
+++ b/src/main/resources/Program_Field_Values_Test8.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219C241E-24AA-4D38-806E-DBFE50C5E726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A4270C-0FCE-41D8-BE76-9463FD37B203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -804,14 +804,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.5703125" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.5546875" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -822,7 +822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -844,7 +844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -855,7 +855,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -866,7 +866,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -877,7 +877,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -888,7 +888,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -922,13 +922,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8AC423-05DF-4280-95EB-279829201824}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -939,7 +939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -950,7 +950,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -961,7 +961,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -972,7 +972,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
       <c r="C5" s="6"/>
     </row>
@@ -984,13 +984,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72FC2E7-798D-4A0D-9033-321F9F52B381}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1042,13 +1042,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4FD98F4-5D65-489F-B6B9-0B173C389D1A}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1155,14 +1155,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE56BC4D-8AEC-4E4E-85C8-89449AEEC07A}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1303,14 +1303,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CAF4D77-609A-474F-A16C-8985A05DDF89}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1351,13 +1351,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA29119-FFAC-4260-A292-75CB58842AAB}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1409,14 +1409,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD981C06-1D14-46F5-A3A9-915937C2A139}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1512,9 +1512,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DEDBD1-53EB-4D57-9108-0852043B1383}">
   <dimension ref="A2:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -1632,13 +1632,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1669,14 +1669,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="33.85546875" customWidth="1"/>
-    <col min="3" max="3" width="56.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="33.88671875" customWidth="1"/>
+    <col min="3" max="3" width="56.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1728,14 +1728,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB7E775-FC9D-4F7A-8132-7FE7649A7A48}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
-    <col min="2" max="2" width="33.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.5546875" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1886,14 +1886,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C20002D2-73D8-4767-9B06-FA8D83AF8B94}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" customWidth="1"/>
-    <col min="3" max="3" width="46.42578125" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="40.109375" customWidth="1"/>
+    <col min="3" max="3" width="46.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1990,14 +1990,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE65A359-5AAB-4789-BD03-7AE892333B23}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" customWidth="1"/>
-    <col min="2" max="2" width="35.5703125" customWidth="1"/>
-    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35.5546875" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -2082,13 +2082,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B07CBE-222D-4AEE-8FCA-38CFE50B7B5A}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2129,13 +2129,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DC0711-B086-4AFD-A039-B2CBB4A4E899}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2275,13 +2275,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2D24CD-6391-4318-8144-E561BCF57A37}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Program_Field_Values_Test8.xlsx
+++ b/src/main/resources/Program_Field_Values_Test8.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A4270C-0FCE-41D8-BE76-9463FD37B203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95862EEF-4160-4F94-BDB6-CDE4702A6A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="2820" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>

--- a/src/main/resources/Program_Field_Values_Test8.xlsx
+++ b/src/main/resources/Program_Field_Values_Test8.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95862EEF-4160-4F94-BDB6-CDE4702A6A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC113CD3-C982-4F58-8ECA-BFAE466EFBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="2820" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="141">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -257,21 +257,9 @@
     <t>fieldProjectTitle__c</t>
   </si>
   <si>
-    <t>GrantAbbreviation__c</t>
-  </si>
-  <si>
     <t>GA</t>
   </si>
   <si>
-    <t>ProjectPeriodStartDate__c</t>
-  </si>
-  <si>
-    <t>ProjectPeriodEndDate__c</t>
-  </si>
-  <si>
-    <t>BudgetCategoryPackage__c</t>
-  </si>
-  <si>
     <t>Construction</t>
   </si>
   <si>
@@ -281,24 +269,6 @@
     <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
   </si>
   <si>
-    <t>Automation Permanent Internal Program</t>
-  </si>
-  <si>
-    <t>ExternalOrganization__c</t>
-  </si>
-  <si>
-    <t>IsBuildUpFunctionality__c</t>
-  </si>
-  <si>
-    <t>RiskAssessmentRequired__c</t>
-  </si>
-  <si>
-    <t>GrantAwardDescription__c</t>
-  </si>
-  <si>
-    <t>BudgetPeriodEndDate__c</t>
-  </si>
-  <si>
     <t>11/29/2020 06:36 PM</t>
   </si>
   <si>
@@ -444,13 +414,58 @@
   </si>
   <si>
     <t>fieldProgram__c</t>
+  </si>
+  <si>
+    <t>fieldGrantAbbreviation__c</t>
+  </si>
+  <si>
+    <t>fieldProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldBudgetCategoryPackage__c</t>
+  </si>
+  <si>
+    <t>fieldExternalOrganization__c</t>
+  </si>
+  <si>
+    <t>fieldLaverageAllowed__c</t>
+  </si>
+  <si>
+    <t>fieldIsProgramIncomeAnticipated__c</t>
+  </si>
+  <si>
+    <t>fieldIsAdvancePermitted__c</t>
+  </si>
+  <si>
+    <t>fieldRiskAssessmentRequired__c</t>
+  </si>
+  <si>
+    <t>fieldWBSRequired__c</t>
+  </si>
+  <si>
+    <t>fieldIsBuildUpFunctionality__c</t>
+  </si>
+  <si>
+    <t>fieldAreExpensesBuildIUpLevel__c</t>
+  </si>
+  <si>
+    <t>fieldIsMatchRequired__c</t>
+  </si>
+  <si>
+    <t>fieldGrantAwardDescription__c</t>
+  </si>
+  <si>
+    <t>fieldBudgetPeriodEndDate__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,6 +498,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -505,7 +526,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -522,6 +543,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -827,7 +849,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -838,7 +860,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -849,7 +871,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
@@ -860,7 +882,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -871,7 +893,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -882,7 +904,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -893,7 +915,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -904,7 +926,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C9">
         <v>365</v>
@@ -1067,7 +1089,7 @@
         <v>72</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1075,10 +1097,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" t="s">
         <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1086,7 +1108,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1097,7 +1119,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1108,10 +1130,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1119,10 +1141,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1130,10 +1152,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1141,14 +1163,15 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1157,7 +1180,7 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
@@ -1178,7 +1201,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -1189,7 +1212,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -1200,7 +1223,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
@@ -1211,7 +1234,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -1222,7 +1245,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1233,7 +1256,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -1244,7 +1267,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -1255,7 +1278,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -1266,7 +1289,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -1277,7 +1300,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -1288,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -1325,8 +1348,8 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>85</v>
+      <c r="B2" s="8" t="s">
+        <v>139</v>
       </c>
       <c r="C2" t="s">
         <v>45</v>
@@ -1336,8 +1359,8 @@
       <c r="A3" t="s">
         <v>40</v>
       </c>
-      <c r="B3" t="s">
-        <v>86</v>
+      <c r="B3" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="C3">
         <v>3650</v>
@@ -1345,6 +1368,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1373,10 +1397,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1384,7 +1408,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
         <v>50</v>
@@ -1395,10 +1419,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1432,7 +1456,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1443,7 +1467,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1454,10 +1478,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1465,10 +1489,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1476,10 +1500,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1487,10 +1511,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1498,10 +1522,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1530,10 +1554,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1541,10 +1565,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1552,10 +1576,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1563,10 +1587,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1574,10 +1598,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1585,10 +1609,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1596,10 +1620,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1607,10 +1631,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1618,10 +1642,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1931,7 +1955,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -2118,7 +2142,7 @@
         <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2300,7 +2324,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2319,7 +2343,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2330,7 +2354,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C5">
         <v>3650</v>
